--- a/reportes/Reporte_GALLARA MARIA CECILIA.xlsx
+++ b/reportes/Reporte_GALLARA MARIA CECILIA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="70">
   <si>
     <t>N.º DE COMPROBANTE</t>
   </si>
@@ -73,6 +73,9 @@
     <t>74482220590984</t>
   </si>
   <si>
+    <t>74532859389185</t>
+  </si>
+  <si>
     <t>73482867698552</t>
   </si>
   <si>
@@ -133,6 +136,9 @@
     <t>74492421951894</t>
   </si>
   <si>
+    <t>74532856070325</t>
+  </si>
+  <si>
     <t>20/08/2024</t>
   </si>
   <si>
@@ -155,6 +161,9 @@
   </si>
   <si>
     <t>01/12/2024</t>
+  </si>
+  <si>
+    <t>01/01/2025</t>
   </si>
   <si>
     <t>01/04/2024</t>
@@ -584,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="1" customWidth="1"/>
@@ -638,19 +647,19 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F2" s="3">
         <v>41558.28</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -667,19 +676,19 @@
         <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F3" s="3">
         <v>527138.84</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -696,19 +705,19 @@
         <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F4" s="3">
         <v>147156.81</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -725,19 +734,19 @@
         <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F5" s="3">
         <v>154514.65</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -754,19 +763,19 @@
         <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F6" s="3">
         <v>297710.2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -783,19 +792,19 @@
         <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F7" s="3">
         <v>292446.17</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -812,19 +821,19 @@
         <v>16</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F8" s="3">
         <v>297710.2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -841,19 +850,19 @@
         <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F9" s="3">
         <v>300687.3</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -870,24 +879,24 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F10" s="3">
         <v>300687.3</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1">
-        <v>241</v>
+        <v>297</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>9</v>
@@ -899,24 +908,24 @@
         <v>19</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F11" s="3">
-        <v>147156.81</v>
+        <v>307654.34</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>9</v>
@@ -928,24 +937,24 @@
         <v>20</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F12" s="3">
-        <v>154514.65</v>
+        <v>147156.81</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>9</v>
@@ -957,24 +966,24 @@
         <v>21</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F13" s="3">
-        <v>203959.34</v>
+        <v>154514.65</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>9</v>
@@ -986,24 +995,24 @@
         <v>22</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F14" s="3">
-        <v>24475.12</v>
+        <v>203959.34</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>9</v>
@@ -1015,24 +1024,24 @@
         <v>23</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F15" s="3">
-        <v>228434.46</v>
+        <v>24475.12</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>9</v>
@@ -1044,24 +1053,24 @@
         <v>24</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F16" s="3">
-        <v>27412.13</v>
+        <v>228434.46</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="1">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>9</v>
@@ -1073,24 +1082,24 @@
         <v>25</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F17" s="3">
-        <v>255846.59</v>
+        <v>27412.13</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="1">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -1102,24 +1111,24 @@
         <v>26</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F18" s="3">
-        <v>22514.5</v>
+        <v>255846.59</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="1">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>9</v>
@@ -1131,24 +1140,24 @@
         <v>27</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F19" s="3">
-        <v>278361.09</v>
+        <v>22514.5</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="1">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>9</v>
@@ -1160,24 +1169,24 @@
         <v>28</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F20" s="3">
-        <v>286711.93</v>
+        <v>278361.09</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="1">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>9</v>
@@ -1189,24 +1198,24 @@
         <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F21" s="3">
-        <v>8350.84</v>
+        <v>286711.93</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="1">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>9</v>
@@ -1218,24 +1227,24 @@
         <v>30</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F22" s="3">
-        <v>292446.17</v>
+        <v>8350.84</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="1">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>9</v>
@@ -1247,24 +1256,24 @@
         <v>31</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F23" s="3">
-        <v>5734.24</v>
+        <v>292446.17</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="1">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>9</v>
@@ -1276,24 +1285,24 @@
         <v>32</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="F24" s="3">
-        <v>5262.03</v>
+        <v>5734.24</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="1">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>9</v>
@@ -1308,21 +1317,21 @@
         <v>44</v>
       </c>
       <c r="F25" s="3">
-        <v>297710.2</v>
+        <v>5262.03</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="1">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>9</v>
@@ -1334,24 +1343,24 @@
         <v>34</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F26" s="3">
-        <v>2977.1</v>
+        <v>297710.2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="1">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>9</v>
@@ -1363,24 +1372,24 @@
         <v>35</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F27" s="3">
-        <v>300687.3</v>
+        <v>2977.1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="1">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>9</v>
@@ -1392,24 +1401,24 @@
         <v>36</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F28" s="3">
         <v>300687.3</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="1">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>9</v>
@@ -1421,24 +1430,24 @@
         <v>37</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F29" s="3">
-        <v>5436.42</v>
+        <v>300687.3</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="1">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>9</v>
@@ -1450,19 +1459,77 @@
         <v>38</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F30" s="3">
+        <v>5436.42</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="1">
+        <v>292</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="1">
+        <v>3</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F31" s="3">
         <v>3006.87</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>66</v>
+      <c r="G31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="1">
+        <v>296</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="1">
+        <v>3</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" s="3">
+        <v>307654.34</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
